--- a/data/comparativa-titanium.xlsx
+++ b/data/comparativa-titanium.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Pecho y Hombro de Pie Black Series</t>
+          <t>Multipress 3 Funciones Black Series</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>https://www.titaniumstrength.es/selectorizada-pecho-y-hombro-de-pie.html</t>
+          <t>https://www.titaniumstrength.es/titanium-strength-black-series-multipress-3-funciones.html</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Misma doble función, pero Titanium trabaja de pie</t>
+          <t>Cubre pecho y hombro, pero añade una tercera función y no es idéntica</t>
         </is>
       </c>
     </row>

--- a/data/comparativa-titanium.xlsx
+++ b/data/comparativa-titanium.xlsx
@@ -1732,18 +1732,38 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Sin equivalente</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="8" t="n"/>
+          <t>Directa</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Dual Pecho y Hombro de Pie Elite Series</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>1895</v>
+      </c>
+      <c r="G2" s="4">
+        <f>C2-F2</f>
+        <v/>
+      </c>
+      <c r="H2" s="6">
+        <f>G2/F2</f>
+        <v/>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>https://www.titaniumstrength.es/selectorizada-dual-pecho-y-hombro-de-pie.html</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>Black Series ofrece ambas funciones en máquinas separadas, no en una única dual equivalente</t>
+          <t>Caso especial: ellos la tienen en Elite y nosotros en Pro Series, por eso el par cruza de gama</t>
         </is>
       </c>
     </row>
